--- a/src/src/main/webapp/portal/zkb/zkbFePartOrder/excel/APM_ZKB_FePartOrder_Batch_Return_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/zkbFePartOrder/excel/APM_ZKB_FePartOrder_Batch_Return_Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23801"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503202755\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workspaces\NewProject\hc-apm-web\src\src\main\webapp\portal\zkb\zkbFePartOrder\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82E8782A-5909-49AD-9F9B-F34939D011A1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E48FF8B-5D79-4A73-9AC7-F086E9C6D8A6}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
   <sheets>
     <sheet name="备件归还" sheetId="2" r:id="rId1"/>
@@ -88,25 +88,27 @@
     <t>合同类型</t>
   </si>
   <si>
+    <t>订单编号</t>
+  </si>
+  <si>
+    <t>已经归还数量</t>
+  </si>
+  <si>
+    <t>Part Serial Number</t>
+  </si>
+  <si>
+    <t>故障描述</t>
+  </si>
+  <si>
+    <t>归还日期</t>
+  </si>
+  <si>
+    <t>归还数量</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>归还备注</t>
-  </si>
-  <si>
-    <t>归还数量</t>
-  </si>
-  <si>
-    <t>订单编号</t>
-  </si>
-  <si>
-    <t>已经归还数量</t>
-  </si>
-  <si>
-    <t>Part Serial Number</t>
-  </si>
-  <si>
-    <t>故障描述</t>
-  </si>
-  <si>
-    <t>归还日期</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -114,13 +116,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -128,6 +130,15 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="1"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -153,10 +164,10 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -172,7 +183,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -469,24 +480,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFD4DBF4-FEF1-4385-BAD9-BD07A4FA541B}">
   <dimension ref="A1:P1"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.1"/>
   <cols>
-    <col min="1" max="1" width="21.21875" customWidth="1"/>
-    <col min="2" max="2" width="27.77734375" customWidth="1"/>
-    <col min="3" max="3" width="26.33203125" customWidth="1"/>
-    <col min="4" max="4" width="31.21875" customWidth="1"/>
-    <col min="5" max="5" width="25.6640625" customWidth="1"/>
-    <col min="6" max="9" width="20.21875" customWidth="1"/>
-    <col min="10" max="10" width="18.44140625" customWidth="1"/>
-    <col min="11" max="11" width="15.109375" customWidth="1"/>
+    <col min="1" max="1" width="21.19921875" customWidth="1"/>
+    <col min="2" max="2" width="27.796875" customWidth="1"/>
+    <col min="3" max="3" width="26.34765625" customWidth="1"/>
+    <col min="4" max="4" width="31.19921875" customWidth="1"/>
+    <col min="5" max="5" width="25.6484375" customWidth="1"/>
+    <col min="6" max="9" width="20.19921875" customWidth="1"/>
+    <col min="10" max="10" width="18.44921875" customWidth="1"/>
+    <col min="11" max="11" width="15.09765625" customWidth="1"/>
     <col min="12" max="12" width="16" customWidth="1"/>
-    <col min="13" max="13" width="19.21875" customWidth="1"/>
-    <col min="14" max="14" width="28.6640625" customWidth="1"/>
-    <col min="15" max="15" width="21.21875" customWidth="1"/>
-    <col min="16" max="16" width="19.77734375" customWidth="1"/>
+    <col min="13" max="13" width="19.19921875" customWidth="1"/>
+    <col min="14" max="14" width="28.6484375" customWidth="1"/>
+    <col min="15" max="15" width="19.796875" customWidth="1"/>
+    <col min="16" max="16" width="21.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15">
+    <row r="1" spans="1:16" ht="14.7">
       <c r="A1" s="1" t="s">
         <v>14</v>
       </c>
@@ -503,7 +514,7 @@
         <v>10</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>12</v>
@@ -524,24 +535,25 @@
         <v>0</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N1048576" xr:uid="{5EF74CF9-6898-4782-B426-3B5C29500DFA}">
       <formula1>"坏还,好还,DOA,Wrong Part,Short Life,cancel"</formula1>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P1048576" xr:uid="{BEE146B8-B84E-48C2-8748-6B364BB3C64C}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O1:O1048576" xr:uid="{BEE146B8-B84E-48C2-8748-6B364BB3C64C}">
       <formula1>1</formula1>
       <formula2>1000</formula2>
     </dataValidation>
@@ -554,27 +566,27 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1A9004E-0524-4CCC-A26D-ED41880F2076}">
   <dimension ref="A1:T1"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.1"/>
   <cols>
-    <col min="1" max="1" width="20.5546875" customWidth="1"/>
-    <col min="2" max="2" width="22.6640625" customWidth="1"/>
-    <col min="3" max="3" width="21.5546875" customWidth="1"/>
-    <col min="4" max="6" width="30.21875" customWidth="1"/>
-    <col min="7" max="7" width="21.5546875" customWidth="1"/>
-    <col min="8" max="8" width="22.109375" customWidth="1"/>
-    <col min="9" max="9" width="22.88671875" customWidth="1"/>
-    <col min="10" max="10" width="21.77734375" customWidth="1"/>
-    <col min="11" max="11" width="18.77734375" customWidth="1"/>
-    <col min="12" max="12" width="17.88671875" customWidth="1"/>
-    <col min="13" max="13" width="19.5546875" customWidth="1"/>
-    <col min="14" max="16" width="20.44140625" customWidth="1"/>
+    <col min="1" max="1" width="20.546875" customWidth="1"/>
+    <col min="2" max="2" width="22.6484375" customWidth="1"/>
+    <col min="3" max="3" width="21.546875" customWidth="1"/>
+    <col min="4" max="6" width="30.19921875" customWidth="1"/>
+    <col min="7" max="7" width="21.546875" customWidth="1"/>
+    <col min="8" max="8" width="22.09765625" customWidth="1"/>
+    <col min="9" max="9" width="22.8984375" customWidth="1"/>
+    <col min="10" max="10" width="21.796875" customWidth="1"/>
+    <col min="11" max="11" width="18.796875" customWidth="1"/>
+    <col min="12" max="12" width="17.8984375" customWidth="1"/>
+    <col min="13" max="13" width="19.546875" customWidth="1"/>
+    <col min="14" max="16" width="20.44921875" customWidth="1"/>
     <col min="17" max="17" width="26" customWidth="1"/>
-    <col min="18" max="18" width="22.77734375" style="2" customWidth="1"/>
-    <col min="19" max="19" width="23.44140625" customWidth="1"/>
-    <col min="20" max="20" width="18.6640625" customWidth="1"/>
+    <col min="18" max="18" width="22.796875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="23.44921875" customWidth="1"/>
+    <col min="20" max="20" width="18.6484375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15">
+    <row r="1" spans="1:20" ht="14.7">
       <c r="A1" s="1" t="s">
         <v>14</v>
       </c>
@@ -591,7 +603,7 @@
         <v>10</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -618,16 +630,16 @@
         <v>7</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="S1" s="1" t="s">
         <v>9</v>
@@ -637,6 +649,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N1048576" xr:uid="{92F051A3-932B-4571-805C-57526BB3A954}">
       <formula1>"坏还,好还,DOA,Wrong Part,Short Life,cancel"</formula1>
